--- a/data/internalStats2/File1/RPT_RPT9853920998378DH_internalStats2.xlsx
+++ b/data/internalStats2/File1/RPT_RPT9853920998378DH_internalStats2.xlsx
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="P10" s="162" t="n">
-        <v>55133.69350794561</v>
+        <v>55133.6935079456</v>
       </c>
       <c r="Q10" s="163" t="n">
         <v>0</v>
@@ -2224,7 +2224,7 @@
         <v>49.58452074664683</v>
       </c>
       <c r="T10" s="161" t="n">
-        <v>55183.27802869226</v>
+        <v>55183.27802869225</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" thickBot="1">
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="P11" s="165" t="n">
-        <v>1364.8686034661</v>
+        <v>1364.868603466101</v>
       </c>
       <c r="Q11" s="166" t="n">
         <v>0</v>
@@ -2246,7 +2246,7 @@
         <v>196.5042335394999</v>
       </c>
       <c r="T11" s="168" t="n">
-        <v>1561.3728370056</v>
+        <v>1561.372837005601</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" thickBot="1">
@@ -2594,10 +2594,10 @@
         <v>79339.75577026585</v>
       </c>
       <c r="T25" s="72" t="n">
-        <v>34.07302870312816</v>
+        <v>34.07302870312817</v>
       </c>
       <c r="U25" s="179" t="n">
-        <v>0.2146478085129739</v>
+        <v>0.214647808512974</v>
       </c>
       <c r="W25" s="175" t="n">
         <v>1</v>
@@ -2663,7 +2663,7 @@
         <v>9212.535368124589</v>
       </c>
       <c r="Q26" s="186" t="n">
-        <v>0.08309480698666272</v>
+        <v>0.08309480698666274</v>
       </c>
       <c r="R26" s="185" t="n">
         <v>1193.081652027774</v>
@@ -2741,7 +2741,7 @@
         <v>8622.353500927462</v>
       </c>
       <c r="Q27" s="186" t="n">
-        <v>0.07777151145702429</v>
+        <v>0.07777151145702431</v>
       </c>
       <c r="R27" s="185" t="n">
         <v>1192.30014280217</v>
@@ -2816,13 +2816,13 @@
         </is>
       </c>
       <c r="P28" s="185" t="n">
-        <v>5520.587381943595</v>
+        <v>5520.587381943594</v>
       </c>
       <c r="Q28" s="186" t="n">
         <v>0.04979434266736427</v>
       </c>
       <c r="R28" s="185" t="n">
-        <v>605.745548086862</v>
+        <v>605.7455480868618</v>
       </c>
       <c r="S28" s="187" t="n">
         <v>7909.979579883866</v>
@@ -2897,7 +2897,7 @@
         <v>5512.525795291357</v>
       </c>
       <c r="Q29" s="186" t="n">
-        <v>0.04972162913519248</v>
+        <v>0.04972162913519249</v>
       </c>
       <c r="R29" s="185" t="n">
         <v>1249.337230175964</v>
@@ -3111,7 +3111,7 @@
         <v>3146.661061732651</v>
       </c>
       <c r="Q32" s="186" t="n">
-        <v>0.02838211014980884</v>
+        <v>0.02838211014980885</v>
       </c>
       <c r="R32" s="185" t="n">
         <v>462.0261522616343</v>
@@ -3195,7 +3195,7 @@
         <v>686.7171412839099</v>
       </c>
       <c r="S33" s="187" t="n">
-        <v>6398.884314999522</v>
+        <v>6398.88431499952</v>
       </c>
       <c r="T33" s="84" t="n">
         <v>4.506520365848544</v>
@@ -3345,7 +3345,7 @@
         <v>2620.638717236338</v>
       </c>
       <c r="Q35" s="186" t="n">
-        <v>0.02363751776128692</v>
+        <v>0.02363751776128693</v>
       </c>
       <c r="R35" s="185" t="n">
         <v>345.2870647997254</v>
@@ -3792,7 +3792,7 @@
         </is>
       </c>
       <c r="P41" s="185" t="n">
-        <v>1561.3728370056</v>
+        <v>1561.372837005601</v>
       </c>
       <c r="Q41" s="186" t="n">
         <v>0.01408319961235711</v>
@@ -3801,7 +3801,7 @@
         <v>359.6397669043586</v>
       </c>
       <c r="S41" s="187" t="n">
-        <v>8959.159919944088</v>
+        <v>8959.159919944086</v>
       </c>
       <c r="T41" s="84" t="n">
         <v>4.341491071594501</v>
@@ -3881,7 +3881,7 @@
         <v>208.4980829583808</v>
       </c>
       <c r="S42" s="187" t="n">
-        <v>5964.419580898266</v>
+        <v>5964.419580898265</v>
       </c>
       <c r="T42" s="84" t="n">
         <v>7.487248693337843</v>
@@ -6049,7 +6049,7 @@
         <v>0</v>
       </c>
       <c r="AB75" s="190" t="n">
-        <v>9267.033172801768</v>
+        <v>9267.033172801766</v>
       </c>
     </row>
     <row r="76">
@@ -6840,7 +6840,7 @@
         <v>0</v>
       </c>
       <c r="AB87" s="190" t="n">
-        <v>1710.998070478463</v>
+        <v>1710.998070478462</v>
       </c>
     </row>
     <row r="88">
@@ -7524,7 +7524,7 @@
         <v>3184.536013900853</v>
       </c>
       <c r="Q100" s="186" t="n">
-        <v>0.05770835165401138</v>
+        <v>0.05770835165401139</v>
       </c>
       <c r="R100" s="185" t="n">
         <v>962.3076730454776</v>
@@ -7599,7 +7599,7 @@
         <v>2679.807060116694</v>
       </c>
       <c r="Q101" s="186" t="n">
-        <v>0.0485619404255641</v>
+        <v>0.04856194042556411</v>
       </c>
       <c r="R101" s="185" t="n">
         <v>843.652101957246</v>
@@ -8050,7 +8050,7 @@
         <v>804.2544769804459</v>
       </c>
       <c r="Q107" s="186" t="n">
-        <v>0.01457424251894347</v>
+        <v>0.01457424251894348</v>
       </c>
       <c r="R107" s="185" t="n">
         <v>828.1048616851064</v>
@@ -8200,7 +8200,7 @@
         <v>498.1725488015753</v>
       </c>
       <c r="Q109" s="186" t="n">
-        <v>0.009027599783806845</v>
+        <v>0.009027599783806847</v>
       </c>
       <c r="R109" s="185" t="n">
         <v>137.146327591756</v>
@@ -8275,7 +8275,7 @@
         <v>331.3032322739321</v>
       </c>
       <c r="Q110" s="186" t="n">
-        <v>0.00600368887295301</v>
+        <v>0.006003688872953011</v>
       </c>
       <c r="R110" s="185" t="n">
         <v>300.3410617405242</v>
@@ -8679,7 +8679,7 @@
         </is>
       </c>
       <c r="P121" s="176" t="n">
-        <v>1561.3728370056</v>
+        <v>1561.372837005601</v>
       </c>
       <c r="Q121" s="177" t="n">
         <v>1</v>
@@ -8688,7 +8688,7 @@
         <v>359.6397669043586</v>
       </c>
       <c r="S121" s="178" t="n">
-        <v>8959.159919944088</v>
+        <v>8959.159919944086</v>
       </c>
       <c r="T121" s="72" t="n">
         <v>4.341491071594501</v>
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="O147" s="239" t="n">
-        <v>7437.956592937452</v>
+        <v>7437.956592937451</v>
       </c>
       <c r="P147" s="84" t="n">
         <v>13.63594514274421</v>
@@ -9336,7 +9336,7 @@
         <v>4.506520365848544</v>
       </c>
       <c r="R151" s="240" t="n">
-        <v>6398.884314999521</v>
+        <v>6398.88431499952</v>
       </c>
       <c r="T151" s="172" t="n"/>
       <c r="U151" s="172" t="n"/>
@@ -11646,7 +11646,7 @@
         </is>
       </c>
       <c r="O301" s="239" t="n">
-        <v>7437.956592937452</v>
+        <v>7437.956592937451</v>
       </c>
       <c r="P301" s="84" t="n">
         <v>13.63594514274421</v>
@@ -11743,7 +11743,7 @@
         <v>4.506520365848544</v>
       </c>
       <c r="R305" s="240" t="n">
-        <v>6398.884314999521</v>
+        <v>6398.88431499952</v>
       </c>
     </row>
     <row r="306">
@@ -16988,13 +16988,13 @@
         <v>0</v>
       </c>
       <c r="R8" s="159" t="n">
-        <v>2.577067939231929</v>
+        <v>2.57706793923193</v>
       </c>
       <c r="S8" s="160" t="n">
-        <v>67.72396266545526</v>
+        <v>67.72396266545532</v>
       </c>
       <c r="T8" s="161" t="n">
-        <v>27015.54591925719</v>
+        <v>27015.5459192572</v>
       </c>
     </row>
     <row r="9">
@@ -17010,10 +17010,10 @@
         <v>0</v>
       </c>
       <c r="R9" s="163" t="n">
-        <v>22.90282108124559</v>
+        <v>22.9028210812456</v>
       </c>
       <c r="S9" s="164" t="n">
-        <v>65.46234229720312</v>
+        <v>65.46234229720314</v>
       </c>
       <c r="T9" s="161" t="n">
         <v>26812.52920243434</v>
@@ -17035,7 +17035,7 @@
         <v>0</v>
       </c>
       <c r="S10" s="164" t="n">
-        <v>72.64476754058381</v>
+        <v>72.6447675405838</v>
       </c>
       <c r="T10" s="161" t="n">
         <v>65063.45466590601</v>
@@ -17060,7 +17060,7 @@
         <v>249.9950540643609</v>
       </c>
       <c r="T11" s="168" t="n">
-        <v>1753.298172230914</v>
+        <v>1753.298172230913</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" thickBot="1">
@@ -17076,7 +17076,7 @@
         <v>0</v>
       </c>
       <c r="R12" s="166" t="n">
-        <v>25.47988902047752</v>
+        <v>25.47988902047753</v>
       </c>
       <c r="S12" s="167" t="n">
         <v>455.8261265676031</v>
@@ -17555,7 +17555,7 @@
         <v>8558.030471186486</v>
       </c>
       <c r="Q27" s="186" t="n">
-        <v>0.07093574267465561</v>
+        <v>0.07093574267465559</v>
       </c>
       <c r="R27" s="185" t="n">
         <v>1232.714110456642</v>
@@ -17708,13 +17708,13 @@
         </is>
       </c>
       <c r="P29" s="185" t="n">
-        <v>5758.614189381809</v>
+        <v>5758.61418938181</v>
       </c>
       <c r="Q29" s="186" t="n">
-        <v>0.04773196072109511</v>
+        <v>0.04773196072109512</v>
       </c>
       <c r="R29" s="185" t="n">
-        <v>629.9102787609263</v>
+        <v>629.9102787609264</v>
       </c>
       <c r="S29" s="187" t="n">
         <v>8154.317491039048</v>
@@ -17789,7 +17789,7 @@
         <v>4648.157765468977</v>
       </c>
       <c r="Q30" s="186" t="n">
-        <v>0.0385276173381978</v>
+        <v>0.03852761733819779</v>
       </c>
       <c r="R30" s="185" t="n">
         <v>1007.0360290917</v>
@@ -18003,7 +18003,7 @@
         <v>3140.191975803396</v>
       </c>
       <c r="Q33" s="186" t="n">
-        <v>0.02602840112506934</v>
+        <v>0.02602840112506933</v>
       </c>
       <c r="R33" s="185" t="n">
         <v>490.4806047028345</v>
@@ -18081,7 +18081,7 @@
         <v>2847.999563655173</v>
       </c>
       <c r="Q34" s="186" t="n">
-        <v>0.02360647871787328</v>
+        <v>0.02360647871787327</v>
       </c>
       <c r="R34" s="185" t="n">
         <v>0</v>
@@ -18237,7 +18237,7 @@
         <v>2715.913463332387</v>
       </c>
       <c r="Q36" s="186" t="n">
-        <v>0.02251164438011976</v>
+        <v>0.02251164438011975</v>
       </c>
       <c r="R36" s="185" t="n">
         <v>400.1116667756391</v>
@@ -18312,13 +18312,13 @@
         </is>
       </c>
       <c r="P37" s="185" t="n">
-        <v>2317.698464537464</v>
+        <v>2317.698464537465</v>
       </c>
       <c r="Q37" s="186" t="n">
-        <v>0.01921092270370012</v>
+        <v>0.01921092270370013</v>
       </c>
       <c r="R37" s="185" t="n">
-        <v>476.4659102433905</v>
+        <v>476.4659102433906</v>
       </c>
       <c r="S37" s="187" t="n">
         <v>3497.290207285741</v>
@@ -18526,16 +18526,16 @@
         </is>
       </c>
       <c r="P40" s="185" t="n">
-        <v>1753.298172230914</v>
+        <v>1753.298172230913</v>
       </c>
       <c r="Q40" s="186" t="n">
-        <v>0.01453272553726643</v>
+        <v>0.01453272553726642</v>
       </c>
       <c r="R40" s="185" t="n">
-        <v>393.6207395081463</v>
+        <v>393.6207395081462</v>
       </c>
       <c r="S40" s="187" t="n">
-        <v>9700.002168606865</v>
+        <v>9700.002168606863</v>
       </c>
       <c r="T40" s="84" t="n">
         <v>4.454283009634526</v>
@@ -18849,7 +18849,7 @@
         <v>825.4853483728185</v>
       </c>
       <c r="Q44" s="207" t="n">
-        <v>0.00684227713970203</v>
+        <v>0.006842277139702028</v>
       </c>
       <c r="R44" s="206" t="n">
         <v>414.6972528919617</v>
@@ -19069,7 +19069,7 @@
         <v>9087.296923728383</v>
       </c>
       <c r="Q49" s="177" t="n">
-        <v>0.3363728777085636</v>
+        <v>0.3363728777085634</v>
       </c>
       <c r="R49" s="176" t="n">
         <v>567.3010511639239</v>
@@ -19133,7 +19133,7 @@
         <v>3140.191975803396</v>
       </c>
       <c r="Q50" s="186" t="n">
-        <v>0.1162364804764137</v>
+        <v>0.1162364804764136</v>
       </c>
       <c r="R50" s="185" t="n">
         <v>490.4806047028345</v>
@@ -19293,7 +19293,7 @@
         <v>2295.663320808904</v>
       </c>
       <c r="Q52" s="186" t="n">
-        <v>0.08497564060597095</v>
+        <v>0.08497564060597092</v>
       </c>
       <c r="R52" s="185" t="n">
         <v>376.6692492661692</v>
@@ -19443,7 +19443,7 @@
         <v>1738.171527956644</v>
       </c>
       <c r="Q54" s="186" t="n">
-        <v>0.06433967809318421</v>
+        <v>0.06433967809318419</v>
       </c>
       <c r="R54" s="185" t="n">
         <v>446.6604974173617</v>
@@ -19668,7 +19668,7 @@
         <v>825.4853483728185</v>
       </c>
       <c r="Q57" s="186" t="n">
-        <v>0.03055593808246521</v>
+        <v>0.0305559380824652</v>
       </c>
       <c r="R57" s="185" t="n">
         <v>414.6972528919617</v>
@@ -19743,7 +19743,7 @@
         <v>798.7798250534602</v>
       </c>
       <c r="Q58" s="186" t="n">
-        <v>0.02956741379355487</v>
+        <v>0.02956741379355486</v>
       </c>
       <c r="R58" s="185" t="n">
         <v>646.020788007232</v>
@@ -20118,7 +20118,7 @@
         <v>164.3013003104025</v>
       </c>
       <c r="Q63" s="186" t="n">
-        <v>0.00608173163708994</v>
+        <v>0.006081731637089939</v>
       </c>
       <c r="R63" s="185" t="n">
         <v>125.2186189598836</v>
@@ -20193,7 +20193,7 @@
         <v>80.28978246687787</v>
       </c>
       <c r="Q64" s="186" t="n">
-        <v>0.00297198445320499</v>
+        <v>0.002971984453204989</v>
       </c>
       <c r="R64" s="185" t="n">
         <v>18.52354606116344</v>
@@ -20688,7 +20688,7 @@
         <v>6003.864457264311</v>
       </c>
       <c r="Q74" s="186" t="n">
-        <v>0.2239201088392368</v>
+        <v>0.2239201088392367</v>
       </c>
       <c r="R74" s="185" t="n">
         <v>1300.753573203689</v>
@@ -21063,7 +21063,7 @@
         <v>1422.770089705869</v>
       </c>
       <c r="Q79" s="186" t="n">
-        <v>0.05306362853589712</v>
+        <v>0.05306362853589711</v>
       </c>
       <c r="R79" s="185" t="n">
         <v>1591.517696511745</v>
@@ -23383,16 +23383,16 @@
         </is>
       </c>
       <c r="P121" s="176" t="n">
-        <v>1753.298172230914</v>
+        <v>1753.298172230913</v>
       </c>
       <c r="Q121" s="177" t="n">
         <v>1</v>
       </c>
       <c r="R121" s="176" t="n">
-        <v>393.6207395081463</v>
+        <v>393.6207395081462</v>
       </c>
       <c r="S121" s="178" t="n">
-        <v>9700.002168606865</v>
+        <v>9700.002168606863</v>
       </c>
       <c r="T121" s="72" t="n">
         <v>4.454283009634526</v>
@@ -23935,7 +23935,7 @@
         </is>
       </c>
       <c r="O147" s="239" t="n">
-        <v>5758.614189381809</v>
+        <v>5758.61418938181</v>
       </c>
       <c r="P147" s="84" t="n">
         <v>9.940678841032806</v>
@@ -24016,7 +24016,7 @@
         <v>4.775784957707994</v>
       </c>
       <c r="R150" s="240" t="n">
-        <v>6781.217652820743</v>
+        <v>6781.217652820742</v>
       </c>
       <c r="T150" s="172" t="n"/>
       <c r="U150" s="172" t="n"/>
@@ -24079,10 +24079,10 @@
         </is>
       </c>
       <c r="O153" s="239" t="n">
-        <v>2317.698464537464</v>
+        <v>2317.698464537465</v>
       </c>
       <c r="P153" s="84" t="n">
-        <v>6.0497311890091</v>
+        <v>6.049731189009099</v>
       </c>
       <c r="Q153" s="84" t="n">
         <v>4.864353177656564</v>
@@ -24610,7 +24610,7 @@
         <v>0</v>
       </c>
       <c r="R178" s="240" t="n">
-        <v>7696.942306693135</v>
+        <v>7696.942306693134</v>
       </c>
       <c r="T178" s="172" t="n"/>
       <c r="U178" s="172" t="n"/>
@@ -25043,7 +25043,7 @@
         <v>0</v>
       </c>
       <c r="R202" s="240" t="n">
-        <v>2648.90429592809</v>
+        <v>2648.904295928089</v>
       </c>
       <c r="T202" s="172" t="n"/>
       <c r="U202" s="172" t="n"/>
@@ -26350,7 +26350,7 @@
         </is>
       </c>
       <c r="O301" s="239" t="n">
-        <v>5758.614189381809</v>
+        <v>5758.61418938181</v>
       </c>
       <c r="P301" s="84" t="n">
         <v>9.940678841032806</v>
@@ -26425,7 +26425,7 @@
         <v>4.775784957707994</v>
       </c>
       <c r="R304" s="240" t="n">
-        <v>6781.217652820743</v>
+        <v>6781.217652820742</v>
       </c>
     </row>
     <row r="305">
@@ -26482,10 +26482,10 @@
         </is>
       </c>
       <c r="O307" s="239" t="n">
-        <v>2317.698464537464</v>
+        <v>2317.698464537465</v>
       </c>
       <c r="P307" s="84" t="n">
-        <v>6.0497311890091</v>
+        <v>6.049731189009099</v>
       </c>
       <c r="Q307" s="84" t="n">
         <v>4.864353177656564</v>
@@ -26866,7 +26866,7 @@
         <v>0</v>
       </c>
       <c r="R327" s="240" t="n">
-        <v>7696.942306693135</v>
+        <v>7696.942306693134</v>
       </c>
     </row>
     <row r="328">
@@ -27229,7 +27229,7 @@
         <v>0</v>
       </c>
       <c r="R350" s="240" t="n">
-        <v>2648.90429592809</v>
+        <v>2648.904295928089</v>
       </c>
     </row>
     <row r="351">
@@ -31771,7 +31771,7 @@
         <v>0</v>
       </c>
       <c r="S9" s="164" t="n">
-        <v>73.77876919115967</v>
+        <v>73.77876919115965</v>
       </c>
       <c r="T9" s="161" t="n">
         <v>28828.09121400122</v>
@@ -31793,7 +31793,7 @@
         <v>0</v>
       </c>
       <c r="S10" s="164" t="n">
-        <v>105.8607103958014</v>
+        <v>105.8607103958013</v>
       </c>
       <c r="T10" s="161" t="n">
         <v>76309.81224507983</v>
@@ -31806,7 +31806,7 @@
         </is>
       </c>
       <c r="P11" s="165" t="n">
-        <v>1691.719304215407</v>
+        <v>1691.719304215406</v>
       </c>
       <c r="Q11" s="166" t="n">
         <v>0</v>
@@ -31837,7 +31837,7 @@
         <v>0</v>
       </c>
       <c r="S12" s="167" t="n">
-        <v>517.3233776238113</v>
+        <v>517.3233776238112</v>
       </c>
       <c r="T12" s="168" t="n">
         <v>134038.8891955273</v>
@@ -32316,13 +32316,13 @@
         <v>0.06470191646833921</v>
       </c>
       <c r="R27" s="185" t="n">
-        <v>1301.263566880429</v>
+        <v>1301.263566880428</v>
       </c>
       <c r="S27" s="187" t="n">
         <v>16782.17516149627</v>
       </c>
       <c r="T27" s="84" t="n">
-        <v>6.664732059646523</v>
+        <v>6.664732059646524</v>
       </c>
       <c r="U27" s="188" t="n">
         <v>0.04415590822282003</v>
@@ -32951,7 +32951,7 @@
         <v>0</v>
       </c>
       <c r="AB35" s="190" t="n">
-        <v>7860.324361552335</v>
+        <v>7860.324361552336</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" thickTop="1">
@@ -35596,7 +35596,7 @@
         <v>1571.314728403774</v>
       </c>
       <c r="Q76" s="186" t="n">
-        <v>0.05450637424237849</v>
+        <v>0.0545063742423785</v>
       </c>
       <c r="R76" s="185" t="n">
         <v>818.2927051357549</v>
@@ -35746,7 +35746,7 @@
         <v>1536.379945536515</v>
       </c>
       <c r="Q78" s="186" t="n">
-        <v>0.05329454295573778</v>
+        <v>0.05329454295573779</v>
       </c>
       <c r="R78" s="185" t="n">
         <v>650.5954683531687</v>
@@ -35896,7 +35896,7 @@
         <v>1285.215825748591</v>
       </c>
       <c r="Q80" s="186" t="n">
-        <v>0.04458206463299895</v>
+        <v>0.04458206463299896</v>
       </c>
       <c r="R80" s="185" t="n">
         <v>1064.71973903936</v>
@@ -38696,13 +38696,13 @@
         <v>6048.064903563136</v>
       </c>
       <c r="P147" s="84" t="n">
-        <v>9.374396464881981</v>
+        <v>9.374396464881979</v>
       </c>
       <c r="Q147" s="84" t="n">
         <v>9.146347533057741</v>
       </c>
       <c r="R147" s="240" t="n">
-        <v>8610.69043506082</v>
+        <v>8610.690435060822</v>
       </c>
       <c r="T147" s="172" t="n"/>
       <c r="U147" s="172" t="n"/>
@@ -39368,7 +39368,7 @@
         <v>0</v>
       </c>
       <c r="R178" s="240" t="n">
-        <v>7860.324361552335</v>
+        <v>7860.324361552336</v>
       </c>
       <c r="T178" s="172" t="n"/>
       <c r="U178" s="172" t="n"/>
@@ -39504,7 +39504,7 @@
         <v>0</v>
       </c>
       <c r="P185" s="84" t="n">
-        <v>0.3861512108415192</v>
+        <v>0.3861512108415193</v>
       </c>
       <c r="Q185" s="84" t="n">
         <v>0</v>
@@ -41111,13 +41111,13 @@
         <v>6048.064903563136</v>
       </c>
       <c r="P301" s="84" t="n">
-        <v>9.374396464881981</v>
+        <v>9.374396464881979</v>
       </c>
       <c r="Q301" s="84" t="n">
         <v>9.146347533057741</v>
       </c>
       <c r="R301" s="240" t="n">
-        <v>8610.69043506082</v>
+        <v>8610.690435060822</v>
       </c>
     </row>
     <row r="302">
@@ -41624,7 +41624,7 @@
         <v>0</v>
       </c>
       <c r="R327" s="240" t="n">
-        <v>7860.324361552335</v>
+        <v>7860.324361552336</v>
       </c>
     </row>
     <row r="328">
@@ -41746,7 +41746,7 @@
         <v>0</v>
       </c>
       <c r="P334" s="84" t="n">
-        <v>0.3861512108415192</v>
+        <v>0.3861512108415193</v>
       </c>
       <c r="Q334" s="84" t="n">
         <v>0</v>
@@ -44837,7 +44837,7 @@
         <v>0</v>
       </c>
       <c r="AO617" s="190" t="n">
-        <v>7860.324361552335</v>
+        <v>7860.324361552336</v>
       </c>
     </row>
     <row r="618">
@@ -45671,10 +45671,10 @@
         </is>
       </c>
       <c r="AM652" s="84" t="n">
-        <v>0.3861512108415192</v>
+        <v>0.3861512108415193</v>
       </c>
       <c r="AN652" s="189" t="n">
-        <v>0.002558371030290641</v>
+        <v>0.002558371030290642</v>
       </c>
       <c r="AO652" s="190" t="n">
         <v>339.8745718075103</v>
@@ -46498,7 +46498,7 @@
         </is>
       </c>
       <c r="P8" s="158" t="n">
-        <v>24625.45604667848</v>
+        <v>24625.45604667849</v>
       </c>
       <c r="Q8" s="159" t="n">
         <v>0</v>
@@ -46510,7 +46510,7 @@
         <v>13.97742347567033</v>
       </c>
       <c r="T8" s="161" t="n">
-        <v>24639.43347015415</v>
+        <v>24639.43347015416</v>
       </c>
     </row>
     <row r="9">
@@ -46529,7 +46529,7 @@
         <v>0</v>
       </c>
       <c r="S9" s="164" t="n">
-        <v>79.8432552694123</v>
+        <v>79.84325526941235</v>
       </c>
       <c r="T9" s="161" t="n">
         <v>30927.87689821089</v>
@@ -46542,7 +46542,7 @@
         </is>
       </c>
       <c r="P10" s="162" t="n">
-        <v>89690.13459538278</v>
+        <v>89690.1345953828</v>
       </c>
       <c r="Q10" s="163" t="n">
         <v>0</v>
@@ -46554,7 +46554,7 @@
         <v>181.1296569509379</v>
       </c>
       <c r="T10" s="161" t="n">
-        <v>89871.26425233373</v>
+        <v>89871.26425233374</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" thickBot="1">
@@ -46595,10 +46595,10 @@
         <v>0</v>
       </c>
       <c r="S12" s="167" t="n">
-        <v>636.6383285347703</v>
+        <v>636.6383285347704</v>
       </c>
       <c r="T12" s="168" t="n">
-        <v>147648.0641845762</v>
+        <v>147648.0641845763</v>
       </c>
     </row>
     <row r="13"/>
@@ -46915,7 +46915,7 @@
         <v>78816.00626191396</v>
       </c>
       <c r="Q25" s="177" t="n">
-        <v>0.5338099533996282</v>
+        <v>0.5338099533996281</v>
       </c>
       <c r="R25" s="176" t="n">
         <v>1278.180270252493</v>
@@ -46993,7 +46993,7 @@
         <v>11957.11386915134</v>
       </c>
       <c r="Q26" s="186" t="n">
-        <v>0.08098388512702502</v>
+        <v>0.08098388512702499</v>
       </c>
       <c r="R26" s="185" t="n">
         <v>1352.765962052527</v>
@@ -47071,7 +47071,7 @@
         <v>8676.100013225549</v>
       </c>
       <c r="Q27" s="186" t="n">
-        <v>0.0587620302449714</v>
+        <v>0.05876203024497139</v>
       </c>
       <c r="R27" s="185" t="n">
         <v>1356.034136040362</v>
@@ -47149,7 +47149,7 @@
         <v>7177.156153383478</v>
       </c>
       <c r="Q28" s="186" t="n">
-        <v>0.04860988996382131</v>
+        <v>0.0486098899638213</v>
       </c>
       <c r="R28" s="185" t="n">
         <v>1420.976010268078</v>
@@ -47227,7 +47227,7 @@
         <v>6254.517428753081</v>
       </c>
       <c r="Q29" s="186" t="n">
-        <v>0.04236098497664181</v>
+        <v>0.0423609849766418</v>
       </c>
       <c r="R29" s="185" t="n">
         <v>686.0358204215186</v>
@@ -47305,7 +47305,7 @@
         <v>5628.852136237471</v>
       </c>
       <c r="Q30" s="186" t="n">
-        <v>0.03812344013668063</v>
+        <v>0.03812344013668062</v>
       </c>
       <c r="R30" s="185" t="n">
         <v>1114.43358344224</v>
@@ -47369,7 +47369,7 @@
         <v>4548.964252200496</v>
       </c>
       <c r="Q31" s="186" t="n">
-        <v>0.03080950825412647</v>
+        <v>0.03080950825412646</v>
       </c>
       <c r="R31" s="185" t="n">
         <v>846.0038993371622</v>
@@ -47441,7 +47441,7 @@
         <v>4548.964252200496</v>
       </c>
       <c r="Q32" s="186" t="n">
-        <v>0.03080950825412647</v>
+        <v>0.03080950825412646</v>
       </c>
       <c r="R32" s="185" t="n">
         <v>846.0038993371622</v>
@@ -47519,7 +47519,7 @@
         <v>4469.377130929079</v>
       </c>
       <c r="Q33" s="186" t="n">
-        <v>0.03027047564498962</v>
+        <v>0.03027047564498961</v>
       </c>
       <c r="R33" s="185" t="n">
         <v>653.2124194089411</v>
@@ -47909,7 +47909,7 @@
         <v>1374.07878237639</v>
       </c>
       <c r="Q38" s="186" t="n">
-        <v>0.009306446311809689</v>
+        <v>0.009306446311809687</v>
       </c>
       <c r="R38" s="185" t="n">
         <v>215.3316853088869</v>
@@ -47973,7 +47973,7 @@
         <v>1208.641034384585</v>
       </c>
       <c r="Q39" s="186" t="n">
-        <v>0.008185959233936529</v>
+        <v>0.008185959233936528</v>
       </c>
       <c r="R39" s="185" t="n">
         <v>438.7530888176663</v>
@@ -48045,7 +48045,7 @@
         <v>884.4130782099252</v>
       </c>
       <c r="Q40" s="186" t="n">
-        <v>0.00599000794960855</v>
+        <v>0.005990007949608549</v>
       </c>
       <c r="R40" s="185" t="n">
         <v>449.9758725135909</v>
@@ -48125,7 +48125,7 @@
         <v>813.7050826922497</v>
       </c>
       <c r="Q41" s="186" t="n">
-        <v>0.005511112436090116</v>
+        <v>0.005511112436090114</v>
       </c>
       <c r="R41" s="185" t="n">
         <v>346.1316318614575</v>
@@ -48205,7 +48205,7 @@
         <v>543.2691942120091</v>
       </c>
       <c r="Q42" s="186" t="n">
-        <v>0.003679487416325778</v>
+        <v>0.003679487416325777</v>
       </c>
       <c r="R42" s="185" t="n">
         <v>344.3641674305946</v>
@@ -48365,7 +48365,7 @@
         <v>424.8362177620434</v>
       </c>
       <c r="Q44" s="207" t="n">
-        <v>0.00287735718113413</v>
+        <v>0.002877357181134129</v>
       </c>
       <c r="R44" s="206" t="n">
         <v>336.4463923211698</v>
@@ -48585,7 +48585,7 @@
         <v>13959.50943817</v>
       </c>
       <c r="Q49" s="177" t="n">
-        <v>0.5665515587068678</v>
+        <v>0.5665515587068676</v>
       </c>
       <c r="R49" s="176" t="n">
         <v>605.1827412114759</v>
@@ -48734,7 +48734,7 @@
         <v>2231.88452544884</v>
       </c>
       <c r="Q51" s="186" t="n">
-        <v>0.09058181179986673</v>
+        <v>0.0905818117998667</v>
       </c>
       <c r="R51" s="185" t="n">
         <v>332.0016578876662</v>
@@ -48809,7 +48809,7 @@
         <v>2001.340877920067</v>
       </c>
       <c r="Q52" s="186" t="n">
-        <v>0.08122511746645068</v>
+        <v>0.08122511746645067</v>
       </c>
       <c r="R52" s="185" t="n">
         <v>1722.435355282332</v>
@@ -48884,7 +48884,7 @@
         <v>1117.34428273227</v>
       </c>
       <c r="Q53" s="186" t="n">
-        <v>0.0453478073708843</v>
+        <v>0.04534780737088429</v>
       </c>
       <c r="R53" s="185" t="n">
         <v>326.6062097044705</v>
@@ -48959,7 +48959,7 @@
         <v>884.4130782099252</v>
       </c>
       <c r="Q54" s="186" t="n">
-        <v>0.03589421320426131</v>
+        <v>0.0358942132042613</v>
       </c>
       <c r="R54" s="185" t="n">
         <v>449.9758725135909</v>
@@ -49034,7 +49034,7 @@
         <v>813.7050826922497</v>
       </c>
       <c r="Q55" s="186" t="n">
-        <v>0.03302450454787827</v>
+        <v>0.03302450454787826</v>
       </c>
       <c r="R55" s="185" t="n">
         <v>346.1316318614575</v>
@@ -49334,7 +49334,7 @@
         <v>75.88014636804007</v>
       </c>
       <c r="Q59" s="186" t="n">
-        <v>0.003079622202351122</v>
+        <v>0.003079622202351121</v>
       </c>
       <c r="R59" s="185" t="n">
         <v>19.23937797830994</v>
@@ -50556,7 +50556,7 @@
         <v>0</v>
       </c>
       <c r="AB80" s="190" t="n">
-        <v>4334.929426567819</v>
+        <v>4334.929426567818</v>
       </c>
     </row>
     <row r="81">
@@ -51387,7 +51387,7 @@
         <v>51082.33343448647</v>
       </c>
       <c r="Q97" s="177" t="n">
-        <v>0.5683945125225052</v>
+        <v>0.5683945125225051</v>
       </c>
       <c r="R97" s="176" t="n">
         <v>1652.764885833379</v>
@@ -51421,7 +51421,7 @@
         <v>0</v>
       </c>
       <c r="AB97" s="181" t="n">
-        <v>9367.106546647334</v>
+        <v>9367.106546647332</v>
       </c>
     </row>
     <row r="98">
@@ -51537,7 +51537,7 @@
         <v>7233.700896317213</v>
       </c>
       <c r="Q99" s="186" t="n">
-        <v>0.08048958648235965</v>
+        <v>0.08048958648235964</v>
       </c>
       <c r="R99" s="185" t="n">
         <v>1297.697205715482</v>
@@ -51612,7 +51612,7 @@
         <v>4548.964252200496</v>
       </c>
       <c r="Q100" s="186" t="n">
-        <v>0.0506164488732267</v>
+        <v>0.05061644887322669</v>
       </c>
       <c r="R100" s="185" t="n">
         <v>846.0038993371622</v>
@@ -51687,7 +51687,7 @@
         <v>4548.964252200496</v>
       </c>
       <c r="Q101" s="186" t="n">
-        <v>0.0506164488732267</v>
+        <v>0.05061644887322669</v>
       </c>
       <c r="R101" s="185" t="n">
         <v>846.0038993371622</v>
@@ -51721,7 +51721,7 @@
         <v>0</v>
       </c>
       <c r="AB101" s="190" t="n">
-        <v>4334.929426567819</v>
+        <v>4334.929426567818</v>
       </c>
     </row>
     <row r="102">
@@ -51762,7 +51762,7 @@
         <v>4221.639102178104</v>
       </c>
       <c r="Q102" s="186" t="n">
-        <v>0.04697429303236355</v>
+        <v>0.04697429303236354</v>
       </c>
       <c r="R102" s="185" t="n">
         <v>1114.43358344224</v>
@@ -51988,7 +51988,7 @@
         <v>1208.641034384585</v>
       </c>
       <c r="Q105" s="186" t="n">
-        <v>0.01344858163996731</v>
+        <v>0.0134485816399673</v>
       </c>
       <c r="R105" s="185" t="n">
         <v>438.7530888176663</v>
@@ -52213,7 +52213,7 @@
         <v>424.8362177620434</v>
       </c>
       <c r="Q108" s="186" t="n">
-        <v>0.004727164141913264</v>
+        <v>0.004727164141913263</v>
       </c>
       <c r="R108" s="185" t="n">
         <v>336.4463923211698</v>
@@ -52288,7 +52288,7 @@
         <v>63.64211364413745</v>
       </c>
       <c r="Q109" s="186" t="n">
-        <v>0.0007081475282849917</v>
+        <v>0.0007081475282849915</v>
       </c>
       <c r="R109" s="185" t="n">
         <v>1544.930224778733</v>
@@ -53244,10 +53244,10 @@
         <v>87555.74838878366</v>
       </c>
       <c r="P145" s="72" t="n">
-        <v>68.10200542396777</v>
+        <v>68.10200542396778</v>
       </c>
       <c r="Q145" s="72" t="n">
-        <v>68.10200542396777</v>
+        <v>68.10200542396778</v>
       </c>
       <c r="R145" s="238" t="n">
         <v>164416.923215098</v>
@@ -53313,16 +53313,16 @@
         </is>
       </c>
       <c r="O148" s="239" t="n">
-        <v>6254.517428753081</v>
+        <v>6254.51742875308</v>
       </c>
       <c r="P148" s="84" t="n">
-        <v>9.284039392724651</v>
+        <v>9.284039392724653</v>
       </c>
       <c r="Q148" s="84" t="n">
         <v>9.116896294001295</v>
       </c>
       <c r="R148" s="240" t="n">
-        <v>8711.710965408925</v>
+        <v>8711.710965408924</v>
       </c>
       <c r="T148" s="172" t="n"/>
       <c r="U148" s="172" t="n"/>
@@ -53975,7 +53975,7 @@
         <v>0</v>
       </c>
       <c r="R179" s="240" t="n">
-        <v>5978.147288911581</v>
+        <v>5978.14728891158</v>
       </c>
       <c r="T179" s="172" t="n"/>
       <c r="U179" s="172" t="n"/>
@@ -54106,7 +54106,7 @@
         <v>0</v>
       </c>
       <c r="R185" s="240" t="n">
-        <v>4933.735211317693</v>
+        <v>4933.735211317694</v>
       </c>
       <c r="T185" s="172" t="n"/>
       <c r="U185" s="172" t="n"/>
@@ -55663,10 +55663,10 @@
         <v>87555.74838878366</v>
       </c>
       <c r="P299" s="72" t="n">
-        <v>68.10200542396777</v>
+        <v>68.10200542396778</v>
       </c>
       <c r="Q299" s="72" t="n">
-        <v>68.10200542396777</v>
+        <v>68.10200542396778</v>
       </c>
       <c r="R299" s="238" t="n">
         <v>164416.923215098</v>
@@ -55726,16 +55726,16 @@
         </is>
       </c>
       <c r="O302" s="239" t="n">
-        <v>6254.517428753081</v>
+        <v>6254.51742875308</v>
       </c>
       <c r="P302" s="84" t="n">
-        <v>9.284039392724651</v>
+        <v>9.284039392724653</v>
       </c>
       <c r="Q302" s="84" t="n">
         <v>9.116896294001295</v>
       </c>
       <c r="R302" s="240" t="n">
-        <v>8711.710965408925</v>
+        <v>8711.710965408924</v>
       </c>
     </row>
     <row r="303">
@@ -56229,7 +56229,7 @@
         <v>0</v>
       </c>
       <c r="R328" s="240" t="n">
-        <v>5978.147288911581</v>
+        <v>5978.14728891158</v>
       </c>
     </row>
     <row r="329">
@@ -56348,7 +56348,7 @@
         <v>0</v>
       </c>
       <c r="R334" s="240" t="n">
-        <v>4933.735211317693</v>
+        <v>4933.735211317694</v>
       </c>
     </row>
     <row r="335">
@@ -61206,7 +61206,7 @@
         </is>
       </c>
       <c r="P9" s="162" t="n">
-        <v>33099.44482839734</v>
+        <v>33099.44482839735</v>
       </c>
       <c r="Q9" s="163" t="n">
         <v>0</v>
@@ -61215,10 +61215,10 @@
         <v>0</v>
       </c>
       <c r="S9" s="164" t="n">
-        <v>87.27239153339974</v>
+        <v>87.27239153339971</v>
       </c>
       <c r="T9" s="161" t="n">
-        <v>33186.71721993074</v>
+        <v>33186.71721993075</v>
       </c>
     </row>
     <row r="10">
@@ -61228,7 +61228,7 @@
         </is>
       </c>
       <c r="P10" s="162" t="n">
-        <v>95637.05381006612</v>
+        <v>95637.05381006614</v>
       </c>
       <c r="Q10" s="163" t="n">
         <v>0</v>
@@ -61272,7 +61272,7 @@
         </is>
       </c>
       <c r="P12" s="165" t="n">
-        <v>155328.4864763057</v>
+        <v>155328.4864763058</v>
       </c>
       <c r="Q12" s="166" t="n">
         <v>0</v>
@@ -61604,13 +61604,13 @@
         <v>0.625564273411665</v>
       </c>
       <c r="R25" s="176" t="n">
-        <v>1322.000815884655</v>
+        <v>1322.000815884656</v>
       </c>
       <c r="S25" s="178" t="n">
-        <v>178793.5289474547</v>
+        <v>178793.5289474546</v>
       </c>
       <c r="T25" s="72" t="n">
-        <v>73.90391183428737</v>
+        <v>73.90391183428736</v>
       </c>
       <c r="U25" s="179" t="n">
         <v>0.4854146741725145</v>
@@ -62052,16 +62052,16 @@
         </is>
       </c>
       <c r="P31" s="185" t="n">
-        <v>6531.668755170008</v>
+        <v>6531.668755170009</v>
       </c>
       <c r="Q31" s="186" t="n">
-        <v>0.04182124329847066</v>
+        <v>0.04182124329847067</v>
       </c>
       <c r="R31" s="185" t="n">
-        <v>718.7499406568776</v>
+        <v>718.7499406568777</v>
       </c>
       <c r="S31" s="187" t="n">
-        <v>8691.078714336749</v>
+        <v>8691.078714336747</v>
       </c>
       <c r="T31" s="84" t="n">
         <v>9.087539887934609</v>
@@ -64619,7 +64619,7 @@
         <v>17106.59643424521</v>
       </c>
       <c r="Q73" s="177" t="n">
-        <v>0.5154651579690324</v>
+        <v>0.5154651579690323</v>
       </c>
       <c r="R73" s="176" t="n">
         <v>1854.043827386841</v>
@@ -64694,7 +64694,7 @@
         <v>7879.044506212418</v>
       </c>
       <c r="Q74" s="186" t="n">
-        <v>0.2374156037789887</v>
+        <v>0.2374156037789886</v>
       </c>
       <c r="R74" s="185" t="n">
         <v>1491.224414808953</v>
@@ -64769,7 +64769,7 @@
         <v>3943.683091856954</v>
       </c>
       <c r="Q75" s="186" t="n">
-        <v>0.1188331785190408</v>
+        <v>0.1188331785190407</v>
       </c>
       <c r="R75" s="185" t="n">
         <v>1301.897919730594</v>
@@ -64844,7 +64844,7 @@
         <v>1745.210397481001</v>
       </c>
       <c r="Q76" s="186" t="n">
-        <v>0.05258761768798544</v>
+        <v>0.05258761768798543</v>
       </c>
       <c r="R76" s="185" t="n">
         <v>927.0808786020553</v>
@@ -64919,7 +64919,7 @@
         <v>1454.749955972183</v>
       </c>
       <c r="Q77" s="186" t="n">
-        <v>0.0438353075518573</v>
+        <v>0.04383530755185729</v>
       </c>
       <c r="R77" s="185" t="n">
         <v>1839.295037078401</v>
@@ -64994,7 +64994,7 @@
         <v>995.1954983598959</v>
       </c>
       <c r="Q78" s="186" t="n">
-        <v>0.02998776564023083</v>
+        <v>0.02998776564023082</v>
       </c>
       <c r="R78" s="185" t="n">
         <v>1208.826425409853</v>
@@ -67891,7 +67891,7 @@
         </is>
       </c>
       <c r="O148" s="239" t="n">
-        <v>6531.668755170009</v>
+        <v>6531.668755170008</v>
       </c>
       <c r="P148" s="84" t="n">
         <v>9.254144785880076</v>
@@ -68534,7 +68534,7 @@
         <v>0</v>
       </c>
       <c r="P179" s="84" t="n">
-        <v>0.1101668065004473</v>
+        <v>0.1101668065004472</v>
       </c>
       <c r="Q179" s="84" t="n">
         <v>0</v>
@@ -68992,7 +68992,7 @@
         <v>0</v>
       </c>
       <c r="R200" s="240" t="n">
-        <v>526.9557522630023</v>
+        <v>526.9557522630022</v>
       </c>
       <c r="T200" s="172" t="n"/>
       <c r="U200" s="172" t="n"/>
@@ -70304,7 +70304,7 @@
         </is>
       </c>
       <c r="O302" s="239" t="n">
-        <v>6531.668755170009</v>
+        <v>6531.668755170008</v>
       </c>
       <c r="P302" s="84" t="n">
         <v>9.254144785880076</v>
@@ -70788,7 +70788,7 @@
         <v>0</v>
       </c>
       <c r="P328" s="84" t="n">
-        <v>0.1101668065004473</v>
+        <v>0.1101668065004472</v>
       </c>
       <c r="Q328" s="84" t="n">
         <v>0</v>
@@ -71204,7 +71204,7 @@
         <v>0</v>
       </c>
       <c r="R349" s="240" t="n">
-        <v>526.9557522630023</v>
+        <v>526.9557522630022</v>
       </c>
     </row>
     <row r="350">
